--- a/demo/lumeo_fy2026_model.xlsx
+++ b/demo/lumeo_fy2026_model.xlsx
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>IF(B5&gt;0,999,Assumptions!B11/((B4-B3)/12))</f>
+        <f>IF(B5&gt;0,"Profitable",Assumptions!B11/((B4-B3)/12))</f>
         <v/>
       </c>
     </row>
